--- a/ClosedXML.Tests/Resource/Examples/Tables/ResizingTables.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Tables/ResizingTables.xlsx
@@ -508,10 +508,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14.400625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12.875425" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.880625" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10.685425" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.410625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12.935425" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.920625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.705425" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:5">
@@ -696,10 +696,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14.400625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12.875425" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.880625" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10.685425" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.410625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12.935425" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.920625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.705425" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:5">
@@ -890,11 +890,11 @@
   <x:dimension ref="A1:E14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12.195425" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14.400625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12.875425" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.880625" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10.685425" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="12.285425" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.410625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12.935425" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.920625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.705425" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:5">
@@ -1089,11 +1089,11 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14.400625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12.875425" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.880625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.410625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12.935425" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.920625" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="10.685425" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10.705425" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:6">

--- a/ClosedXML.Tests/Resource/Examples/Tables/ResizingTables.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Tables/ResizingTables.xlsx
@@ -529,7 +529,7 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
-      <x:c r="B3" s="0" t="n">
+      <x:c r="B3" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
@@ -538,12 +538,12 @@
       <x:c r="D3" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="n">
+      <x:c r="E3" s="0">
         <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
-      <x:c r="B4" s="0" t="n">
+      <x:c r="B4" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
@@ -552,12 +552,12 @@
       <x:c r="D4" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="n">
+      <x:c r="E4" s="0">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
-      <x:c r="B5" s="0" t="n">
+      <x:c r="B5" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
@@ -566,12 +566,12 @@
       <x:c r="D5" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E5" s="0" t="n">
+      <x:c r="E5" s="0">
         <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
-      <x:c r="B6" s="0" t="n">
+      <x:c r="B6" s="0">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
@@ -580,12 +580,12 @@
       <x:c r="D6" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E6" s="0" t="n">
+      <x:c r="E6" s="0">
         <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
-      <x:c r="B7" s="0" t="n">
+      <x:c r="B7" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
@@ -594,12 +594,12 @@
       <x:c r="D7" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E7" s="0" t="n">
+      <x:c r="E7" s="0">
         <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
-      <x:c r="B8" s="0" t="n">
+      <x:c r="B8" s="0">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
@@ -608,12 +608,12 @@
       <x:c r="D8" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="0" t="n">
+      <x:c r="E8" s="0">
         <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
-      <x:c r="B9" s="0" t="n">
+      <x:c r="B9" s="0">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
@@ -622,12 +622,12 @@
       <x:c r="D9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E9" s="0" t="n">
+      <x:c r="E9" s="0">
         <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
-      <x:c r="B10" s="0" t="n">
+      <x:c r="B10" s="0">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
@@ -636,12 +636,12 @@
       <x:c r="D10" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E10" s="0" t="n">
+      <x:c r="E10" s="0">
         <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
-      <x:c r="B11" s="0" t="n">
+      <x:c r="B11" s="0">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
@@ -650,12 +650,12 @@
       <x:c r="D11" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E11" s="0" t="n">
+      <x:c r="E11" s="0">
         <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
-      <x:c r="B12" s="0" t="n">
+      <x:c r="B12" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
@@ -664,7 +664,7 @@
       <x:c r="D12" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="E12" s="0" t="n">
+      <x:c r="E12" s="0">
         <x:v>74</x:v>
       </x:c>
     </x:row>
@@ -717,7 +717,7 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
-      <x:c r="B3" s="0" t="n">
+      <x:c r="B3" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
@@ -726,12 +726,12 @@
       <x:c r="D3" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="n">
+      <x:c r="E3" s="0">
         <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
-      <x:c r="B4" s="0" t="n">
+      <x:c r="B4" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
@@ -740,12 +740,12 @@
       <x:c r="D4" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="n">
+      <x:c r="E4" s="0">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
-      <x:c r="B5" s="0" t="n">
+      <x:c r="B5" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
@@ -754,12 +754,12 @@
       <x:c r="D5" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E5" s="0" t="n">
+      <x:c r="E5" s="0">
         <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
-      <x:c r="B6" s="0" t="n">
+      <x:c r="B6" s="0">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
@@ -768,12 +768,12 @@
       <x:c r="D6" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E6" s="0" t="n">
+      <x:c r="E6" s="0">
         <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
-      <x:c r="B7" s="0" t="n">
+      <x:c r="B7" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
@@ -782,12 +782,12 @@
       <x:c r="D7" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E7" s="0" t="n">
+      <x:c r="E7" s="0">
         <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
-      <x:c r="B8" s="0" t="n">
+      <x:c r="B8" s="0">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
@@ -796,12 +796,12 @@
       <x:c r="D8" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="0" t="n">
+      <x:c r="E8" s="0">
         <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
-      <x:c r="B9" s="0" t="n">
+      <x:c r="B9" s="0">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
@@ -810,7 +810,7 @@
       <x:c r="D9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E9" s="0" t="n">
+      <x:c r="E9" s="0">
         <x:v>71</x:v>
       </x:c>
     </x:row>
@@ -818,12 +818,12 @@
       <x:c r="B10" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E10" s="0" t="n">
+      <x:c r="E10" s="0">
         <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
-      <x:c r="B11" s="0" t="n">
+      <x:c r="B11" s="0">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
@@ -832,12 +832,12 @@
       <x:c r="D11" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E11" s="0" t="n">
+      <x:c r="E11" s="0">
         <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
-      <x:c r="B12" s="0" t="n">
+      <x:c r="B12" s="0">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
@@ -846,12 +846,12 @@
       <x:c r="D12" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E12" s="0" t="n">
+      <x:c r="E12" s="0">
         <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
-      <x:c r="B13" s="0" t="n">
+      <x:c r="B13" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
@@ -915,7 +915,7 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
-      <x:c r="B3" s="0" t="n">
+      <x:c r="B3" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
@@ -924,12 +924,12 @@
       <x:c r="D3" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="n">
+      <x:c r="E3" s="0">
         <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
-      <x:c r="B4" s="0" t="n">
+      <x:c r="B4" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
@@ -938,12 +938,12 @@
       <x:c r="D4" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="n">
+      <x:c r="E4" s="0">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
-      <x:c r="B5" s="0" t="n">
+      <x:c r="B5" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
@@ -952,12 +952,12 @@
       <x:c r="D5" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E5" s="0" t="n">
+      <x:c r="E5" s="0">
         <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
-      <x:c r="B6" s="0" t="n">
+      <x:c r="B6" s="0">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
@@ -966,12 +966,12 @@
       <x:c r="D6" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E6" s="0" t="n">
+      <x:c r="E6" s="0">
         <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
-      <x:c r="B7" s="0" t="n">
+      <x:c r="B7" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
@@ -980,12 +980,12 @@
       <x:c r="D7" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="E7" s="0" t="n">
+      <x:c r="E7" s="0">
         <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
-      <x:c r="B8" s="0" t="n">
+      <x:c r="B8" s="0">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
@@ -994,12 +994,12 @@
       <x:c r="D8" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="0" t="n">
+      <x:c r="E8" s="0">
         <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
-      <x:c r="B9" s="0" t="n">
+      <x:c r="B9" s="0">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
@@ -1008,12 +1008,12 @@
       <x:c r="D9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E9" s="0" t="n">
+      <x:c r="E9" s="0">
         <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
-      <x:c r="B10" s="0" t="n">
+      <x:c r="B10" s="0">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
@@ -1022,7 +1022,7 @@
       <x:c r="D10" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E10" s="0" t="n">
+      <x:c r="E10" s="0">
         <x:v>72</x:v>
       </x:c>
     </x:row>
@@ -1035,7 +1035,7 @@
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
-      <x:c r="B12" s="0" t="n">
+      <x:c r="B12" s="0">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
@@ -1044,12 +1044,12 @@
       <x:c r="D12" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E12" s="0" t="n">
+      <x:c r="E12" s="0">
         <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
-      <x:c r="B13" s="0" t="n">
+      <x:c r="B13" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
@@ -1114,7 +1114,7 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6">
-      <x:c r="B3" s="0" t="n">
+      <x:c r="B3" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
@@ -1123,12 +1123,12 @@
       <x:c r="D3" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F3" s="0" t="n">
+      <x:c r="F3" s="0">
         <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
-      <x:c r="B4" s="0" t="n">
+      <x:c r="B4" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
@@ -1137,12 +1137,12 @@
       <x:c r="D4" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F4" s="0" t="n">
+      <x:c r="F4" s="0">
         <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
-      <x:c r="B5" s="0" t="n">
+      <x:c r="B5" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
@@ -1151,12 +1151,12 @@
       <x:c r="D5" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="F5" s="0" t="n">
+      <x:c r="F5" s="0">
         <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
-      <x:c r="B6" s="0" t="n">
+      <x:c r="B6" s="0">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
@@ -1165,12 +1165,12 @@
       <x:c r="D6" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="F6" s="0" t="n">
+      <x:c r="F6" s="0">
         <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6">
-      <x:c r="B7" s="0" t="n">
+      <x:c r="B7" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
@@ -1179,12 +1179,12 @@
       <x:c r="D7" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="F7" s="0" t="n">
+      <x:c r="F7" s="0">
         <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
-      <x:c r="B8" s="0" t="n">
+      <x:c r="B8" s="0">
         <x:v>6</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
@@ -1193,12 +1193,12 @@
       <x:c r="D8" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F8" s="0" t="n">
+      <x:c r="F8" s="0">
         <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6">
-      <x:c r="B9" s="0" t="n">
+      <x:c r="B9" s="0">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
@@ -1207,12 +1207,12 @@
       <x:c r="D9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F9" s="0" t="n">
+      <x:c r="F9" s="0">
         <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6">
-      <x:c r="B10" s="0" t="n">
+      <x:c r="B10" s="0">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
@@ -1221,12 +1221,12 @@
       <x:c r="D10" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="F10" s="0" t="n">
+      <x:c r="F10" s="0">
         <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6">
-      <x:c r="B11" s="0" t="n">
+      <x:c r="B11" s="0">
         <x:v>9</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
@@ -1235,12 +1235,12 @@
       <x:c r="D11" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F11" s="0" t="n">
+      <x:c r="F11" s="0">
         <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6">
-      <x:c r="B12" s="0" t="n">
+      <x:c r="B12" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
@@ -1249,7 +1249,7 @@
       <x:c r="D12" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="F12" s="0" t="n">
+      <x:c r="F12" s="0">
         <x:v>74</x:v>
       </x:c>
     </x:row>

--- a/ClosedXML.Tests/Resource/Examples/Tables/ResizingTables.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Tables/ResizingTables.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
     <x:t>Index</x:t>
   </x:si>
@@ -508,10 +508,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14.410625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12.935425" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.920625" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10.705425" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.139196" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11.853482" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.282054" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="9.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:5">
@@ -696,10 +696,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14.410625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12.935425" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.920625" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10.705425" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.139196" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11.853482" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.282054" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="9.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:5">
@@ -890,11 +890,11 @@
   <x:dimension ref="A1:E14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12.285425" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14.410625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12.935425" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.920625" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10.705425" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="11.282054" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.139196" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11.853482" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.282054" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="9.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:5">
@@ -1089,11 +1089,11 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14.410625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12.935425" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.920625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.139196" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11.853482" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.282054" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="10.705425" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:6">

--- a/ClosedXML.Tests/Resource/Examples/Tables/ResizingTables.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Tables/ResizingTables.xlsx
@@ -500,7 +500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -688,7 +688,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -883,7 +883,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -1081,7 +1081,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>

--- a/ClosedXML.Tests/Resource/Examples/Tables/ResizingTables.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Tables/ResizingTables.xlsx
@@ -6,10 +6,10 @@
     <x:workbookView firstSheet="0" activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Sheet1" sheetId="2" r:id="rId2"/>
-    <x:sheet name="Sheet2" sheetId="3" r:id="rId3"/>
-    <x:sheet name="Sheet3" sheetId="4" r:id="rId4"/>
-    <x:sheet name="Sheet4" sheetId="5" r:id="rId5"/>
+    <x:sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <x:sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <x:sheet name="Sheet3" sheetId="3" r:id="rId4"/>
+    <x:sheet name="Sheet4" sheetId="4" r:id="rId5"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>

--- a/ClosedXML.Tests/Resource/Examples/Tables/ResizingTables.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Tables/ResizingTables.xlsx
@@ -1091,8 +1091,7 @@
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="14.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="11.853482" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.282054" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="9.140625" style="0" customWidth="1"/>
+    <x:col min="4" max="5" width="11.282054" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="9.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
